--- a/multi seed generators/second batch/classification/results/aggregated/privacy_mean_sd.xlsx
+++ b/multi seed generators/second batch/classification/results/aggregated/privacy_mean_sd.xlsx
@@ -1199,12 +1199,10 @@
       <c r="H22" s="2" t="n">
         <v>0.9730864197530865</v>
       </c>
-      <c r="I22" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I22" s="2"/>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.973086 ± 0</t>
+          <t xml:space="preserve">0.973086</t>
         </is>
       </c>
       <c r="K22" s="2" t="n">
@@ -1249,12 +1247,10 @@
       <c r="H23" t="n">
         <v>5.509692938076827</v>
       </c>
-      <c r="I23" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I23"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.50969 ± 0</t>
+          <t xml:space="preserve">5.50969</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1299,12 +1295,10 @@
       <c r="H24" s="2" t="n">
         <v>5.509692938076827</v>
       </c>
-      <c r="I24" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I24" s="2"/>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.50969 ± 0</t>
+          <t xml:space="preserve">5.50969</t>
         </is>
       </c>
       <c r="K24" s="2" t="n">
@@ -1349,12 +1343,10 @@
       <c r="H25" t="n">
         <v>5.475858305808768</v>
       </c>
-      <c r="I25" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I25"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.47586 ± 0</t>
+          <t xml:space="preserve">5.47586</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1399,12 +1391,10 @@
       <c r="H26" s="2" t="n">
         <v>0.9066806772855167</v>
       </c>
-      <c r="I26" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I26" s="2"/>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.906681 ± 0</t>
+          <t xml:space="preserve">0.906681</t>
         </is>
       </c>
       <c r="K26" s="2" t="n">
@@ -1449,12 +1439,10 @@
       <c r="H27" t="n">
         <v>1.0</v>
       </c>
-      <c r="I27" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I27"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -1699,12 +1687,10 @@
       <c r="H32" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="I32" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I32" s="2"/>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="K32" s="2" t="n">
@@ -2199,12 +2185,10 @@
       <c r="H42" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="I42" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I42" s="2"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="K42" s="2" t="n">
@@ -3199,12 +3183,10 @@
       <c r="H62" s="2" t="n">
         <v>0.9403245942571785</v>
       </c>
-      <c r="I62" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I62" s="2"/>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.940325 ± 0</t>
+          <t xml:space="preserve">0.940325</t>
         </is>
       </c>
       <c r="K62" s="2" t="n">
@@ -3249,12 +3231,10 @@
       <c r="H63" t="n">
         <v>4.444467035031164</v>
       </c>
-      <c r="I63" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I63"/>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.44447 ± 0</t>
+          <t xml:space="preserve">4.44447</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -3299,12 +3279,10 @@
       <c r="H64" s="2" t="n">
         <v>4.444467035031164</v>
       </c>
-      <c r="I64" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I64" s="2"/>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.44447 ± 0</t>
+          <t xml:space="preserve">4.44447</t>
         </is>
       </c>
       <c r="K64" s="2" t="n">
@@ -3349,12 +3327,10 @@
       <c r="H65" t="n">
         <v>4.253740757046158</v>
       </c>
-      <c r="I65" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I65"/>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.25374 ± 0</t>
+          <t xml:space="preserve">4.25374</t>
         </is>
       </c>
       <c r="K65" t="n">
@@ -3399,12 +3375,10 @@
       <c r="H66" s="2" t="n">
         <v>0.895473612801383</v>
       </c>
-      <c r="I66" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I66" s="2"/>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.895474 ± 0</t>
+          <t xml:space="preserve">0.895474</t>
         </is>
       </c>
       <c r="K66" s="2" t="n">
@@ -5199,12 +5173,10 @@
       <c r="H102" s="2" t="n">
         <v>0.6269135802469137</v>
       </c>
-      <c r="I102" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I102" s="2"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.626914 ± 0</t>
+          <t xml:space="preserve">0.626914</t>
         </is>
       </c>
       <c r="K102" s="2" t="n">
@@ -5249,12 +5221,10 @@
       <c r="H103" t="n">
         <v>4.569163692549475</v>
       </c>
-      <c r="I103" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I103"/>
       <c r="J103" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.56916 ± 0</t>
+          <t xml:space="preserve">4.56916</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -5299,12 +5269,10 @@
       <c r="H104" s="2" t="n">
         <v>4.569163692549475</v>
       </c>
-      <c r="I104" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I104" s="2"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.56916 ± 0</t>
+          <t xml:space="preserve">4.56916</t>
         </is>
       </c>
       <c r="K104" s="2" t="n">
@@ -5349,12 +5317,10 @@
       <c r="H105" t="n">
         <v>4.160603666732447</v>
       </c>
-      <c r="I105" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I105"/>
       <c r="J105" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.1606 ± 0</t>
+          <t xml:space="preserve">4.1606</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -5399,12 +5365,10 @@
       <c r="H106" s="2" t="n">
         <v>0.8875044863435922</v>
       </c>
-      <c r="I106" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I106" s="2"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.887504 ± 0</t>
+          <t xml:space="preserve">0.887504</t>
         </is>
       </c>
       <c r="K106" s="2" t="n">
@@ -7199,12 +7163,10 @@
       <c r="H142" s="2" t="n">
         <v>0.8493827160493826</v>
       </c>
-      <c r="I142" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I142" s="2"/>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.849383 ± 0</t>
+          <t xml:space="preserve">0.849383</t>
         </is>
       </c>
       <c r="K142" s="2" t="n">
@@ -7249,12 +7211,10 @@
       <c r="H143" t="n">
         <v>5.872811690820016</v>
       </c>
-      <c r="I143" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I143"/>
       <c r="J143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.87281 ± 0</t>
+          <t xml:space="preserve">5.87281</t>
         </is>
       </c>
       <c r="K143" t="n">
@@ -7299,12 +7259,10 @@
       <c r="H144" s="2" t="n">
         <v>5.872811690820016</v>
       </c>
-      <c r="I144" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I144" s="2"/>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.87281 ± 0</t>
+          <t xml:space="preserve">5.87281</t>
         </is>
       </c>
       <c r="K144" s="2" t="n">
@@ -7349,12 +7307,10 @@
       <c r="H145" t="n">
         <v>5.995473117786184</v>
       </c>
-      <c r="I145" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I145"/>
       <c r="J145" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.99547 ± 0</t>
+          <t xml:space="preserve">5.99547</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -7399,12 +7355,10 @@
       <c r="H146" s="2" t="n">
         <v>0.8942671116291279</v>
       </c>
-      <c r="I146" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I146" s="2"/>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.894267 ± 0</t>
+          <t xml:space="preserve">0.894267</t>
         </is>
       </c>
       <c r="K146" s="2" t="n">
@@ -9199,12 +9153,10 @@
       <c r="H182" s="2" t="n">
         <v>0.7533333333333334</v>
       </c>
-      <c r="I182" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I182" s="2"/>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.753333 ± 0</t>
+          <t xml:space="preserve">0.753333</t>
         </is>
       </c>
       <c r="K182" s="2" t="n">
@@ -9249,12 +9201,10 @@
       <c r="H183" t="n">
         <v>8.619195854885204</v>
       </c>
-      <c r="I183" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I183"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.6192 ± 0</t>
+          <t xml:space="preserve">8.6192</t>
         </is>
       </c>
       <c r="K183" t="n">
@@ -9299,12 +9249,10 @@
       <c r="H184" s="2" t="n">
         <v>8.619195854885204</v>
       </c>
-      <c r="I184" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I184" s="2"/>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">8.6192 ± 0</t>
+          <t xml:space="preserve">8.6192</t>
         </is>
       </c>
       <c r="K184" s="2" t="n">
@@ -9349,12 +9297,10 @@
       <c r="H185" t="n">
         <v>7.851049455002918</v>
       </c>
-      <c r="I185" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I185"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t xml:space="preserve">7.85105 ± 0</t>
+          <t xml:space="preserve">7.85105</t>
         </is>
       </c>
       <c r="K185" t="n">
@@ -9399,12 +9345,10 @@
       <c r="H186" s="2" t="n">
         <v>0.9227251748135014</v>
       </c>
-      <c r="I186" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I186" s="2"/>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.922725 ± 0</t>
+          <t xml:space="preserve">0.922725</t>
         </is>
       </c>
       <c r="K186" s="2" t="n">
@@ -10199,12 +10143,10 @@
       <c r="H202" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="I202" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I202" s="2"/>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="K202" s="2" t="n">
@@ -11199,12 +11141,10 @@
       <c r="H222" s="2" t="n">
         <v>0.5166666666666666</v>
       </c>
-      <c r="I222" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I222" s="2"/>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.516667 ± 0</t>
+          <t xml:space="preserve">0.516667</t>
         </is>
       </c>
       <c r="K222" s="2" t="n">
@@ -11249,12 +11189,10 @@
       <c r="H223" t="n">
         <v>1004.0766762884629</v>
       </c>
-      <c r="I223" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I223"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004.08 ± 0</t>
+          <t xml:space="preserve">1004.08</t>
         </is>
       </c>
       <c r="K223" t="n">
@@ -11299,12 +11237,10 @@
       <c r="H224" s="2" t="n">
         <v>1004.0766762884629</v>
       </c>
-      <c r="I224" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I224" s="2"/>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1004.08 ± 0</t>
+          <t xml:space="preserve">1004.08</t>
         </is>
       </c>
       <c r="K224" s="2" t="n">
@@ -11349,12 +11285,10 @@
       <c r="H225" t="n">
         <v>1041.435786799589</v>
       </c>
-      <c r="I225" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I225"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t xml:space="preserve">1041.44 ± 0</t>
+          <t xml:space="preserve">1041.44</t>
         </is>
       </c>
       <c r="K225" t="n">
@@ -11399,12 +11333,10 @@
       <c r="H226" s="2" t="n">
         <v>0.9377329116226886</v>
       </c>
-      <c r="I226" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I226" s="2"/>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.937733 ± 0</t>
+          <t xml:space="preserve">0.937733</t>
         </is>
       </c>
       <c r="K226" s="2" t="n">
@@ -13199,12 +13131,10 @@
       <c r="H262" s="2" t="n">
         <v>0.5151851851851852</v>
       </c>
-      <c r="I262" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I262" s="2"/>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.515185 ± 0</t>
+          <t xml:space="preserve">0.515185</t>
         </is>
       </c>
       <c r="K262" s="2" t="n">
@@ -13249,12 +13179,10 @@
       <c r="H263" t="n">
         <v>3.2184854003164154</v>
       </c>
-      <c r="I263" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I263"/>
       <c r="J263" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.21849 ± 0</t>
+          <t xml:space="preserve">3.21849</t>
         </is>
       </c>
       <c r="K263" t="n">
@@ -13299,12 +13227,10 @@
       <c r="H264" s="2" t="n">
         <v>3.2184854003164154</v>
       </c>
-      <c r="I264" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I264" s="2"/>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.21849 ± 0</t>
+          <t xml:space="preserve">3.21849</t>
         </is>
       </c>
       <c r="K264" s="2" t="n">
@@ -13349,12 +13275,10 @@
       <c r="H265" t="n">
         <v>3.123835628485976</v>
       </c>
-      <c r="I265" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I265"/>
       <c r="J265" t="inlineStr">
         <is>
-          <t xml:space="preserve">3.12384 ± 0</t>
+          <t xml:space="preserve">3.12384</t>
         </is>
       </c>
       <c r="K265" t="n">
@@ -13399,12 +13323,10 @@
       <c r="H266" s="2" t="n">
         <v>0.9164697607326696</v>
       </c>
-      <c r="I266" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I266" s="2"/>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.91647 ± 0</t>
+          <t xml:space="preserve">0.91647</t>
         </is>
       </c>
       <c r="K266" s="2" t="n">
@@ -15199,12 +15121,10 @@
       <c r="H302" s="2" t="n">
         <v>0.4569135802469136</v>
       </c>
-      <c r="I302" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I302" s="2"/>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.456914 ± 0</t>
+          <t xml:space="preserve">0.456914</t>
         </is>
       </c>
       <c r="K302" s="2" t="n">
@@ -15249,12 +15169,10 @@
       <c r="H303" t="n">
         <v>4.794378129434814</v>
       </c>
-      <c r="I303" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I303"/>
       <c r="J303" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.79438 ± 0</t>
+          <t xml:space="preserve">4.79438</t>
         </is>
       </c>
       <c r="K303" t="n">
@@ -15299,12 +15217,10 @@
       <c r="H304" s="2" t="n">
         <v>4.794378129434814</v>
       </c>
-      <c r="I304" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I304" s="2"/>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.79438 ± 0</t>
+          <t xml:space="preserve">4.79438</t>
         </is>
       </c>
       <c r="K304" s="2" t="n">
@@ -15349,12 +15265,10 @@
       <c r="H305" t="n">
         <v>4.490672237534019</v>
       </c>
-      <c r="I305" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I305"/>
       <c r="J305" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.49067 ± 0</t>
+          <t xml:space="preserve">4.49067</t>
         </is>
       </c>
       <c r="K305" t="n">
@@ -15399,12 +15313,10 @@
       <c r="H306" s="2" t="n">
         <v>0.923175303851946</v>
       </c>
-      <c r="I306" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I306" s="2"/>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.923175 ± 0</t>
+          <t xml:space="preserve">0.923175</t>
         </is>
       </c>
       <c r="K306" s="2" t="n">
@@ -15699,12 +15611,10 @@
       <c r="H312" s="2" t="n">
         <v>1.0</v>
       </c>
-      <c r="I312" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I312" s="2"/>
       <c r="J312" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="K312" s="2" t="n">
@@ -15949,12 +15859,10 @@
       <c r="H317" t="n">
         <v>1.0</v>
       </c>
-      <c r="I317" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I317"/>
       <c r="J317" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 ± 0</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="K317" t="n">
@@ -17199,12 +17107,10 @@
       <c r="H342" s="2" t="n">
         <v>0.69</v>
       </c>
-      <c r="I342" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I342" s="2"/>
       <c r="J342" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.69 ± 0</t>
+          <t xml:space="preserve">0.69</t>
         </is>
       </c>
       <c r="K342" s="2" t="n">
@@ -17249,12 +17155,10 @@
       <c r="H343" t="n">
         <v>4.906632239160311</v>
       </c>
-      <c r="I343" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I343"/>
       <c r="J343" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.90663 ± 0</t>
+          <t xml:space="preserve">4.90663</t>
         </is>
       </c>
       <c r="K343" t="n">
@@ -17299,12 +17203,10 @@
       <c r="H344" s="2" t="n">
         <v>4.906632239160311</v>
       </c>
-      <c r="I344" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I344" s="2"/>
       <c r="J344" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.90663 ± 0</t>
+          <t xml:space="preserve">4.90663</t>
         </is>
       </c>
       <c r="K344" s="2" t="n">
@@ -17349,12 +17251,10 @@
       <c r="H345" t="n">
         <v>4.706108650190693</v>
       </c>
-      <c r="I345" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I345"/>
       <c r="J345" t="inlineStr">
         <is>
-          <t xml:space="preserve">4.70611 ± 0</t>
+          <t xml:space="preserve">4.70611</t>
         </is>
       </c>
       <c r="K345" t="n">
@@ -17399,12 +17299,10 @@
       <c r="H346" s="2" t="n">
         <v>0.9254573824055353</v>
       </c>
-      <c r="I346" s="2" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="I346" s="2"/>
       <c r="J346" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">0.925457 ± 0</t>
+          <t xml:space="preserve">0.925457</t>
         </is>
       </c>
       <c r="K346" s="2" t="n">
